--- a/data/trans_orig/P16-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2007</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91021</t>
+          <t>92374</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123538</t>
+          <t>123987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137154</t>
+          <t>136264</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169938</t>
+          <t>169827</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>237768</t>
+          <t>239817</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>285752</t>
+          <t>285012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>149472</t>
+          <t>149023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>181989</t>
+          <t>180636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90900</t>
+          <t>91011</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123684</t>
+          <t>124574</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248096</t>
+          <t>248836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>296080</t>
+          <t>294031</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167740</t>
+          <t>167795</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>213552</t>
+          <t>211242</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270874</t>
+          <t>272596</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>314797</t>
+          <t>317656</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>450971</t>
+          <t>453334</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>516827</t>
+          <t>517113</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,87%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>279523</t>
+          <t>281833</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>325335</t>
+          <t>325280</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189152</t>
+          <t>186293</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>233075</t>
+          <t>231353</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>480197</t>
+          <t>479911</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>546053</t>
+          <t>543690</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99922</t>
+          <t>99288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133499</t>
+          <t>134150</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>188113</t>
+          <t>187622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>223557</t>
+          <t>222820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>294514</t>
+          <t>295779</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>346673</t>
+          <t>345533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>185347</t>
+          <t>184696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218924</t>
+          <t>219558</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111855</t>
+          <t>112592</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147299</t>
+          <t>147790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307585</t>
+          <t>308725</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>359744</t>
+          <t>358479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124814</t>
+          <t>126058</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163081</t>
+          <t>160936</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195317</t>
+          <t>196805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>231788</t>
+          <t>233454</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>327326</t>
+          <t>331156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>383440</t>
+          <t>385107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195590</t>
+          <t>197735</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>233857</t>
+          <t>232613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>139668</t>
+          <t>138002</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176139</t>
+          <t>174651</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>346687</t>
+          <t>345020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>402801</t>
+          <t>398971</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>54,64%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82086</t>
+          <t>81248</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>108765</t>
+          <t>109889</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>116233</t>
+          <t>117049</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144367</t>
+          <t>145216</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>206118</t>
+          <t>205753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>246374</t>
+          <t>246946</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94543</t>
+          <t>93419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121222</t>
+          <t>122060</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63301</t>
+          <t>62452</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91435</t>
+          <t>90619</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>164602</t>
+          <t>164030</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>204858</t>
+          <t>205223</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94160</t>
+          <t>93078</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>125652</t>
+          <t>124011</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>163974</t>
+          <t>162697</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>195235</t>
+          <t>193674</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>266022</t>
+          <t>265589</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>313372</t>
+          <t>313349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,08%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>145159</t>
+          <t>146800</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>176651</t>
+          <t>177733</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82909</t>
+          <t>84470</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>114170</t>
+          <t>115447</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235583</t>
+          <t>235606</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>282933</t>
+          <t>283366</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,62%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>213737</t>
+          <t>214671</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>265498</t>
+          <t>265293</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>330460</t>
+          <t>329231</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>381332</t>
+          <t>377489</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>557817</t>
+          <t>560412</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>631661</t>
+          <t>626134</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,96%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>349529</t>
+          <t>349734</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>401290</t>
+          <t>400356</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>256887</t>
+          <t>260730</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>307759</t>
+          <t>308988</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>621585</t>
+          <t>627112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>695429</t>
+          <t>692834</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>304787</t>
+          <t>303241</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>358629</t>
+          <t>355842</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>414972</t>
+          <t>415371</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>475040</t>
+          <t>469816</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>735191</t>
+          <t>736059</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>813002</t>
+          <t>813169</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,28%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>384148</t>
+          <t>386935</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>437990</t>
+          <t>439536</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>308471</t>
+          <t>313695</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>368539</t>
+          <t>368140</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>713286</t>
+          <t>713119</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>791097</t>
+          <t>790229</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,77%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1273254</t>
+          <t>1278406</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1384974</t>
+          <t>1386547</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1917351</t>
+          <t>1921725</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2039467</t>
+          <t>2034112</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3224177</t>
+          <t>3225281</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3385897</t>
+          <t>3389671</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1890551</t>
+          <t>1888978</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2002271</t>
+          <t>1997119</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1339730</t>
+          <t>1345085</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1461846</t>
+          <t>1457472</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3268825</t>
+          <t>3265051</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3430545</t>
+          <t>3429441</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2012</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2012 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>147605</t>
+          <t>149910</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>184382</t>
+          <t>184168</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>207787</t>
+          <t>206403</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>237605</t>
+          <t>236981</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>364946</t>
+          <t>366205</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>412100</t>
+          <t>412608</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108627</t>
+          <t>108841</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145404</t>
+          <t>143099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49640</t>
+          <t>50264</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79458</t>
+          <t>80842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168154</t>
+          <t>167646</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215308</t>
+          <t>214049</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>235824</t>
+          <t>236584</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>283004</t>
+          <t>282648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>354272</t>
+          <t>353452</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>394410</t>
+          <t>396379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>597897</t>
+          <t>601505</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>665057</t>
+          <t>664426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,62%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>222523</t>
+          <t>222879</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>269703</t>
+          <t>268943</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128321</t>
+          <t>126352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>168459</t>
+          <t>169279</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>363201</t>
+          <t>363832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>430361</t>
+          <t>426753</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156321</t>
+          <t>155386</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>192212</t>
+          <t>192176</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>241746</t>
+          <t>241378</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>274797</t>
+          <t>274814</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>407067</t>
+          <t>409437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>457072</t>
+          <t>459226</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130904</t>
+          <t>130940</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166795</t>
+          <t>167730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66223</t>
+          <t>66206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99274</t>
+          <t>99642</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207064</t>
+          <t>204910</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>257069</t>
+          <t>254699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>161835</t>
+          <t>165406</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202861</t>
+          <t>203138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>272043</t>
+          <t>271872</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>305714</t>
+          <t>305170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>443386</t>
+          <t>442434</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>501357</t>
+          <t>497207</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,25%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171121</t>
+          <t>170844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>212147</t>
+          <t>208576</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82260</t>
+          <t>82804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115931</t>
+          <t>116102</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260599</t>
+          <t>264749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318570</t>
+          <t>319522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98917</t>
+          <t>98542</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128597</t>
+          <t>128783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>166585</t>
+          <t>165906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>190276</t>
+          <t>188964</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272537</t>
+          <t>272891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>311748</t>
+          <t>312331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>83835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>113701</t>
+          <t>114076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29315</t>
+          <t>30627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53006</t>
+          <t>53685</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120461</t>
+          <t>119878</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>159672</t>
+          <t>159318</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>145070</t>
+          <t>143580</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>177426</t>
+          <t>177929</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>203402</t>
+          <t>203666</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>230343</t>
+          <t>230371</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>357804</t>
+          <t>356645</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>402188</t>
+          <t>400236</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,36%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96555</t>
+          <t>96052</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>128911</t>
+          <t>130401</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48797</t>
+          <t>48769</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75738</t>
+          <t>75474</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>150933</t>
+          <t>152885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>195317</t>
+          <t>196476</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>320626</t>
+          <t>318090</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>375287</t>
+          <t>373540</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>442165</t>
+          <t>443162</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>495810</t>
+          <t>494117</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>774889</t>
+          <t>777088</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>849521</t>
+          <t>851981</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,8%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>287501</t>
+          <t>289248</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>342162</t>
+          <t>344698</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>198043</t>
+          <t>199736</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>251688</t>
+          <t>250691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>507120</t>
+          <t>504660</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>581752</t>
+          <t>579553</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,72%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>295905</t>
+          <t>294470</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>355068</t>
+          <t>351411</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>458470</t>
+          <t>454562</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>514706</t>
+          <t>510694</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>767190</t>
+          <t>766437</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>847425</t>
+          <t>849587</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>421904</t>
+          <t>425561</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>481067</t>
+          <t>482502</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>309147</t>
+          <t>313159</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>365383</t>
+          <t>369291</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>753400</t>
+          <t>751238</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>833635</t>
+          <t>834388</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,12%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1667748</t>
+          <t>1659947</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1784240</t>
+          <t>1782840</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2440594</t>
+          <t>2442542</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2553846</t>
+          <t>2556228</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4130658</t>
+          <t>4142304</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4301986</t>
+          <t>4302665</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,67%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1637754</t>
+          <t>1639154</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1754246</t>
+          <t>1762047</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1001561</t>
+          <t>999179</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1114813</t>
+          <t>1112865</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2675415</t>
+          <t>2674736</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2846743</t>
+          <t>2835097</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2016</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>154820</t>
+          <t>155839</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>190548</t>
+          <t>189302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>185620</t>
+          <t>183163</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>217103</t>
+          <t>214976</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>351424</t>
+          <t>349229</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>399728</t>
+          <t>396714</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,11%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103213</t>
+          <t>104459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>138941</t>
+          <t>137922</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71600</t>
+          <t>73727</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103083</t>
+          <t>105540</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>182736</t>
+          <t>185750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231040</t>
+          <t>233235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>220354</t>
+          <t>218938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>267859</t>
+          <t>266306</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>327673</t>
+          <t>328196</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>370579</t>
+          <t>370044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>558442</t>
+          <t>559791</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>622709</t>
+          <t>626653</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>234716</t>
+          <t>236269</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>282221</t>
+          <t>283637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>152505</t>
+          <t>153040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>195411</t>
+          <t>194888</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402950</t>
+          <t>399006</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>467217</t>
+          <t>465868</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144412</t>
+          <t>143737</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179464</t>
+          <t>177781</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>201980</t>
+          <t>201273</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>237006</t>
+          <t>238682</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>359083</t>
+          <t>358253</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>406556</t>
+          <t>406537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>139101</t>
+          <t>140784</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>174153</t>
+          <t>174828</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99303</t>
+          <t>97627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134329</t>
+          <t>135036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248318</t>
+          <t>248337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295791</t>
+          <t>296621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,29%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>207823</t>
+          <t>206268</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>245204</t>
+          <t>244027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>271718</t>
+          <t>269780</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>305304</t>
+          <t>305037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>487921</t>
+          <t>488019</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>541745</t>
+          <t>540540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124760</t>
+          <t>125937</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162141</t>
+          <t>163696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81979</t>
+          <t>82246</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115565</t>
+          <t>117503</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215502</t>
+          <t>216707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>269326</t>
+          <t>269228</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77246</t>
+          <t>76588</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105257</t>
+          <t>105933</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128116</t>
+          <t>127096</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154538</t>
+          <t>155301</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>213624</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252871</t>
+          <t>253906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>59,07%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105964</t>
+          <t>105288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133975</t>
+          <t>134633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64049</t>
+          <t>63286</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90471</t>
+          <t>91491</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>176937</t>
+          <t>175902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216184</t>
+          <t>215358</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,11%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104607</t>
+          <t>104901</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>137693</t>
+          <t>137822</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>156935</t>
+          <t>157419</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>188694</t>
+          <t>188303</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>270949</t>
+          <t>271770</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>317805</t>
+          <t>317698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,25%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125430</t>
+          <t>125301</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>158516</t>
+          <t>158222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84421</t>
+          <t>84812</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>116180</t>
+          <t>115696</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>218433</t>
+          <t>218540</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>265289</t>
+          <t>264468</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>271691</t>
+          <t>268743</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>326393</t>
+          <t>322623</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>367168</t>
+          <t>369876</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>422350</t>
+          <t>419204</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>651838</t>
+          <t>651688</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>730661</t>
+          <t>729115</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>330165</t>
+          <t>333935</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>384867</t>
+          <t>387815</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>268944</t>
+          <t>272090</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>324126</t>
+          <t>321418</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>617191</t>
+          <t>618737</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>696014</t>
+          <t>696164</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,65%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>349656</t>
+          <t>348945</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>406420</t>
+          <t>405873</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>500172</t>
+          <t>501191</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>556035</t>
+          <t>555813</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>862046</t>
+          <t>863732</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>945147</t>
+          <t>943179</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,77%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>372163</t>
+          <t>372710</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>428927</t>
+          <t>429638</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>270132</t>
+          <t>270354</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>325995</t>
+          <t>324976</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>659603</t>
+          <t>661571</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>742704</t>
+          <t>741018</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,18%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1633568</t>
+          <t>1631591</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1750301</t>
+          <t>1748531</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2232652</t>
+          <t>2246478</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2355591</t>
+          <t>2364311</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3910385</t>
+          <t>3906636</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4079246</t>
+          <t>4069645</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,65%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1644049</t>
+          <t>1645819</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1760782</t>
+          <t>1762759</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1188951</t>
+          <t>1180231</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1311890</t>
+          <t>1298064</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2859646</t>
+          <t>2869247</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3028507</t>
+          <t>3032256</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2023</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>178388</t>
+          <t>178244</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>221602</t>
+          <t>221576</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>198755</t>
+          <t>200210</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228475</t>
+          <t>228296</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>391077</t>
+          <t>392811</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>442756</t>
+          <t>442599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89841</t>
+          <t>89867</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133055</t>
+          <t>133199</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61160</t>
+          <t>61339</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90880</t>
+          <t>89425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158321</t>
+          <t>158478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>210000</t>
+          <t>208266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>230367</t>
+          <t>226551</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>286655</t>
+          <t>286477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>309310</t>
+          <t>311624</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>351040</t>
+          <t>352711</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>551083</t>
+          <t>551150</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>629184</t>
+          <t>624153</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,44%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>231735</t>
+          <t>231913</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>288023</t>
+          <t>291839</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>163251</t>
+          <t>161580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>204981</t>
+          <t>202667</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>403496</t>
+          <t>408527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>481597</t>
+          <t>481530</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>165744</t>
+          <t>166216</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202519</t>
+          <t>202176</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>226901</t>
+          <t>227317</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>256769</t>
+          <t>257553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>405094</t>
+          <t>399940</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>451820</t>
+          <t>450086</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,66%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113531</t>
+          <t>113874</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150306</t>
+          <t>149834</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92359</t>
+          <t>91575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122227</t>
+          <t>121811</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213358</t>
+          <t>215092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>260084</t>
+          <t>265238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,87%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154740</t>
+          <t>154811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>200829</t>
+          <t>202382</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>253259</t>
+          <t>252209</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>371993</t>
+          <t>370893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>427576</t>
+          <t>431461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>566124</t>
+          <t>567050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111728</t>
+          <t>110175</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157817</t>
+          <t>157746</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>103725</t>
+          <t>104825</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>222459</t>
+          <t>223509</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>222150</t>
+          <t>221224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>360698</t>
+          <t>356813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,27%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75760</t>
+          <t>75764</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>98414</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125068</t>
+          <t>124643</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143951</t>
+          <t>144370</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>206944</t>
+          <t>204205</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>236378</t>
+          <t>236593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,07%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80044</t>
+          <t>80328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102982</t>
+          <t>102978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64705</t>
+          <t>64286</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83588</t>
+          <t>84013</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151020</t>
+          <t>150805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>180454</t>
+          <t>183193</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>47,29%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>142456</t>
+          <t>142376</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>171615</t>
+          <t>172504</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>154053</t>
+          <t>152285</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>179278</t>
+          <t>178385</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>302786</t>
+          <t>304706</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>343647</t>
+          <t>342996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98021</t>
+          <t>97132</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127180</t>
+          <t>127260</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77778</t>
+          <t>78671</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103003</t>
+          <t>104771</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>183045</t>
+          <t>183696</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>223906</t>
+          <t>221986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>344960</t>
+          <t>343935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>404723</t>
+          <t>406477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>573388</t>
+          <t>574384</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>746463</t>
+          <t>750678</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>938997</t>
+          <t>936183</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1195540</t>
+          <t>1178153</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>219556</t>
+          <t>217802</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>279319</t>
+          <t>280344</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>102802</t>
+          <t>98587</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>275877</t>
+          <t>274881</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>278004</t>
+          <t>295391</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>534547</t>
+          <t>537361</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>119575</t>
+          <t>118177</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>370530</t>
+          <t>370408</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>346859</t>
+          <t>347674</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>391317</t>
+          <t>393683</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>397722</t>
+          <t>386999</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>755954</t>
+          <t>759340</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,2%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>558190</t>
+          <t>558312</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>809145</t>
+          <t>810543</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>323534</t>
+          <t>321168</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>367992</t>
+          <t>367177</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>887618</t>
+          <t>884232</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1245850</t>
+          <t>1256573</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,45%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1310152</t>
+          <t>1322592</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1859567</t>
+          <t>1860030</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2317771</t>
+          <t>2308673</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2679727</t>
+          <t>2627814</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3634249</t>
+          <t>3690438</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4375000</t>
+          <t>4383430</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1600250</t>
+          <t>1599787</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2149665</t>
+          <t>2137225</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>978871</t>
+          <t>1030784</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1340827</t>
+          <t>1349925</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2743415</t>
+          <t>2734985</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3484166</t>
+          <t>3427977</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92374</t>
+          <t>91196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123987</t>
+          <t>123024</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136264</t>
+          <t>136415</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169827</t>
+          <t>169833</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>239817</t>
+          <t>239760</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>285012</t>
+          <t>284772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>149023</t>
+          <t>149986</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>180636</t>
+          <t>181814</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91011</t>
+          <t>91005</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124574</t>
+          <t>124423</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248836</t>
+          <t>249076</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>294031</t>
+          <t>294088</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,09%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167795</t>
+          <t>165543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>211242</t>
+          <t>210895</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>272596</t>
+          <t>272497</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>317656</t>
+          <t>314948</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>453334</t>
+          <t>453759</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>517113</t>
+          <t>517779</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>281833</t>
+          <t>282180</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>325280</t>
+          <t>327532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>186293</t>
+          <t>189001</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231353</t>
+          <t>231452</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>479911</t>
+          <t>479245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>543690</t>
+          <t>543265</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99288</t>
+          <t>97139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134150</t>
+          <t>132851</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187622</t>
+          <t>189097</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>222820</t>
+          <t>222511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>295779</t>
+          <t>295064</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>345533</t>
+          <t>347158</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>184696</t>
+          <t>185995</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>219558</t>
+          <t>221707</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112592</t>
+          <t>112901</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147790</t>
+          <t>146315</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308725</t>
+          <t>307100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>358479</t>
+          <t>359194</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>126058</t>
+          <t>125847</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160936</t>
+          <t>162770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>196805</t>
+          <t>196771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>233454</t>
+          <t>233567</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>331156</t>
+          <t>333717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>385107</t>
+          <t>386014</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197735</t>
+          <t>195901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>232613</t>
+          <t>232824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138002</t>
+          <t>137889</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174651</t>
+          <t>174685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>345020</t>
+          <t>344113</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>398971</t>
+          <t>396410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,29%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81248</t>
+          <t>81980</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109889</t>
+          <t>110263</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117049</t>
+          <t>117441</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145216</t>
+          <t>145944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>205753</t>
+          <t>207754</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>246946</t>
+          <t>247753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93419</t>
+          <t>93045</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122060</t>
+          <t>121328</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62452</t>
+          <t>61724</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90619</t>
+          <t>90227</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>164030</t>
+          <t>163223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>205223</t>
+          <t>203222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93078</t>
+          <t>93924</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124011</t>
+          <t>126685</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>162697</t>
+          <t>161831</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193674</t>
+          <t>194789</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>265589</t>
+          <t>265864</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>313349</t>
+          <t>312212</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,87%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146800</t>
+          <t>144126</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177733</t>
+          <t>176887</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84470</t>
+          <t>83355</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115447</t>
+          <t>116313</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235606</t>
+          <t>236743</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>283366</t>
+          <t>283091</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>214671</t>
+          <t>214856</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>265293</t>
+          <t>261653</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>329231</t>
+          <t>331374</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>377489</t>
+          <t>378638</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>560412</t>
+          <t>560795</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>626134</t>
+          <t>630917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,34%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>349734</t>
+          <t>353374</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>400356</t>
+          <t>400171</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>260730</t>
+          <t>259581</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>308988</t>
+          <t>306845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>627112</t>
+          <t>622329</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>692834</t>
+          <t>692451</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>303241</t>
+          <t>301334</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>355842</t>
+          <t>356459</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>415371</t>
+          <t>415455</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>469816</t>
+          <t>471455</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>736059</t>
+          <t>734146</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>813169</t>
+          <t>813679</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,31%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>386935</t>
+          <t>386318</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>439536</t>
+          <t>441443</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>313695</t>
+          <t>312056</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>368140</t>
+          <t>368056</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>713119</t>
+          <t>712609</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>790229</t>
+          <t>792142</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,9%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1278406</t>
+          <t>1269227</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1386547</t>
+          <t>1384329</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1921725</t>
+          <t>1919943</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2034112</t>
+          <t>2033055</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3225281</t>
+          <t>3227741</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3389671</t>
+          <t>3384674</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1888978</t>
+          <t>1891196</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1997119</t>
+          <t>2006298</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1345085</t>
+          <t>1346142</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1457472</t>
+          <t>1459254</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3265051</t>
+          <t>3270048</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3429441</t>
+          <t>3426981</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,5%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149910</t>
+          <t>149988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>184168</t>
+          <t>184903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>206403</t>
+          <t>205462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>236981</t>
+          <t>236386</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>366205</t>
+          <t>366276</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>412608</t>
+          <t>413424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,25%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108841</t>
+          <t>108106</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>143099</t>
+          <t>143021</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50264</t>
+          <t>50859</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80842</t>
+          <t>81783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167646</t>
+          <t>166830</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214049</t>
+          <t>213978</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>236584</t>
+          <t>235044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>282648</t>
+          <t>280974</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>353452</t>
+          <t>356178</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>396379</t>
+          <t>398272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601505</t>
+          <t>599210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>664426</t>
+          <t>663034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,48%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>222879</t>
+          <t>224553</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>268943</t>
+          <t>270483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126352</t>
+          <t>124459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>169279</t>
+          <t>166553</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>363832</t>
+          <t>365224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>426753</t>
+          <t>429048</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155386</t>
+          <t>156536</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>192176</t>
+          <t>193315</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>241378</t>
+          <t>242692</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>274814</t>
+          <t>275033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>409437</t>
+          <t>408491</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>459226</t>
+          <t>457089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,82%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130940</t>
+          <t>129801</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>167730</t>
+          <t>166580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66206</t>
+          <t>65987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99642</t>
+          <t>98328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>204910</t>
+          <t>207047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>254699</t>
+          <t>255645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165406</t>
+          <t>161201</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>203138</t>
+          <t>201471</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>271872</t>
+          <t>270330</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>305170</t>
+          <t>305511</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>442434</t>
+          <t>440546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>497207</t>
+          <t>498953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,48%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170844</t>
+          <t>172511</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208576</t>
+          <t>212781</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82804</t>
+          <t>82463</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116102</t>
+          <t>117644</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264749</t>
+          <t>263003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>319522</t>
+          <t>321410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98542</t>
+          <t>97766</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128783</t>
+          <t>128507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>165906</t>
+          <t>166303</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188964</t>
+          <t>190497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272891</t>
+          <t>272749</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>312331</t>
+          <t>311925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,17%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83835</t>
+          <t>84111</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114076</t>
+          <t>114852</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53685</t>
+          <t>53288</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119878</t>
+          <t>120284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>159318</t>
+          <t>159460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>143580</t>
+          <t>144765</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>177929</t>
+          <t>177438</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>203666</t>
+          <t>203501</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>230371</t>
+          <t>230706</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>356645</t>
+          <t>356647</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>400236</t>
+          <t>399576</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,24%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96052</t>
+          <t>96543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>130401</t>
+          <t>129216</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48769</t>
+          <t>48434</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75474</t>
+          <t>75639</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>152885</t>
+          <t>153545</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>196476</t>
+          <t>196474</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>318090</t>
+          <t>319349</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>373540</t>
+          <t>372613</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>443162</t>
+          <t>443223</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>494117</t>
+          <t>494705</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>777088</t>
+          <t>776679</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>851981</t>
+          <t>848812</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,57%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>289248</t>
+          <t>290175</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>344698</t>
+          <t>343439</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>199736</t>
+          <t>199148</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>250691</t>
+          <t>250630</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>504660</t>
+          <t>507829</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>579553</t>
+          <t>579962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>294470</t>
+          <t>296266</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>351411</t>
+          <t>352390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>454562</t>
+          <t>454856</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>510694</t>
+          <t>510345</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>766437</t>
+          <t>763272</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>849587</t>
+          <t>846675</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,89%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>425561</t>
+          <t>424582</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>482502</t>
+          <t>480706</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>313159</t>
+          <t>313508</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>369291</t>
+          <t>368997</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>751238</t>
+          <t>754150</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>834388</t>
+          <t>837553</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1659947</t>
+          <t>1663558</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1782840</t>
+          <t>1785559</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2442542</t>
+          <t>2442617</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2556228</t>
+          <t>2556595</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4142304</t>
+          <t>4138554</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4302665</t>
+          <t>4304306</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1639154</t>
+          <t>1636435</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1762047</t>
+          <t>1758436</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>999179</t>
+          <t>998812</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1112865</t>
+          <t>1112790</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2674736</t>
+          <t>2673095</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2835097</t>
+          <t>2838847</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155839</t>
+          <t>153472</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>189302</t>
+          <t>190421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183163</t>
+          <t>184759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>214976</t>
+          <t>215955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>349229</t>
+          <t>346988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>396714</t>
+          <t>395680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104459</t>
+          <t>103340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137922</t>
+          <t>140289</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73727</t>
+          <t>72748</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105540</t>
+          <t>103944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185750</t>
+          <t>186784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233235</t>
+          <t>235476</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>218938</t>
+          <t>220009</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>266306</t>
+          <t>266040</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>328196</t>
+          <t>330988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>370044</t>
+          <t>373054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>559791</t>
+          <t>563080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>626653</t>
+          <t>629560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,38%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>236269</t>
+          <t>236535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>283637</t>
+          <t>282566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153040</t>
+          <t>150030</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>194888</t>
+          <t>192096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>399006</t>
+          <t>396099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>465868</t>
+          <t>462579</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>143737</t>
+          <t>145273</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>177781</t>
+          <t>180062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>201273</t>
+          <t>203647</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>238682</t>
+          <t>237762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>358253</t>
+          <t>356420</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>406537</t>
+          <t>407462</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140784</t>
+          <t>138503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>174828</t>
+          <t>173292</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97627</t>
+          <t>98547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135036</t>
+          <t>132662</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248337</t>
+          <t>247412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>296621</t>
+          <t>298454</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>206268</t>
+          <t>208083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>244027</t>
+          <t>245890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>269780</t>
+          <t>270143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>305037</t>
+          <t>304110</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>488019</t>
+          <t>488629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>540540</t>
+          <t>541337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,49%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125937</t>
+          <t>124074</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163696</t>
+          <t>161881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82246</t>
+          <t>83173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>117503</t>
+          <t>117140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216707</t>
+          <t>215910</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>269228</t>
+          <t>268618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76588</t>
+          <t>76492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105933</t>
+          <t>105721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>127096</t>
+          <t>127048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>155301</t>
+          <t>155336</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>211692</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>253906</t>
+          <t>251355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,48%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105288</t>
+          <t>105500</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134633</t>
+          <t>134729</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63286</t>
+          <t>63251</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91491</t>
+          <t>91539</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>175902</t>
+          <t>178453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>215358</t>
+          <t>218116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104901</t>
+          <t>105057</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>137822</t>
+          <t>136592</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>157419</t>
+          <t>155434</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>188303</t>
+          <t>188651</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>271770</t>
+          <t>271502</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>317698</t>
+          <t>316815</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,08%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125301</t>
+          <t>126531</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>158222</t>
+          <t>158066</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84812</t>
+          <t>84464</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115696</t>
+          <t>117681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>218540</t>
+          <t>219423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>264468</t>
+          <t>264736</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>268743</t>
+          <t>269194</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>322623</t>
+          <t>323365</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>369876</t>
+          <t>367161</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>419204</t>
+          <t>420460</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>651688</t>
+          <t>653609</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>729115</t>
+          <t>731612</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>333935</t>
+          <t>333193</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>387815</t>
+          <t>387364</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>272090</t>
+          <t>270834</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321418</t>
+          <t>324133</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>618737</t>
+          <t>616240</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>696164</t>
+          <t>694243</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>348945</t>
+          <t>350765</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>405873</t>
+          <t>405844</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>501191</t>
+          <t>500904</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>555813</t>
+          <t>556117</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>863732</t>
+          <t>864339</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>943179</t>
+          <t>944374</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,85%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>372710</t>
+          <t>372739</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>429638</t>
+          <t>427818</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>270354</t>
+          <t>270050</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>324976</t>
+          <t>325263</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>661571</t>
+          <t>660376</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>741018</t>
+          <t>740411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,14%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1631591</t>
+          <t>1631125</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1748531</t>
+          <t>1744987</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2246478</t>
+          <t>2242521</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2364311</t>
+          <t>2360411</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3906636</t>
+          <t>3904331</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4069645</t>
+          <t>4081280</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,82%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1645819</t>
+          <t>1649363</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1762759</t>
+          <t>1763225</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1180231</t>
+          <t>1184131</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1298064</t>
+          <t>1302021</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2869247</t>
+          <t>2857612</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3032256</t>
+          <t>3034561</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>201368</t>
+          <t>202842</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>178244</t>
+          <t>185026</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>221576</t>
+          <t>220033</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>216309</t>
+          <t>230530</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>200210</t>
+          <t>215061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228296</t>
+          <t>242597</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>417676</t>
+          <t>433372</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>392811</t>
+          <t>409539</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>442599</t>
+          <t>455333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>110075</t>
+          <t>116003</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89867</t>
+          <t>98812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133199</t>
+          <t>133819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73326</t>
+          <t>85531</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61339</t>
+          <t>73464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89425</t>
+          <t>101000</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>183401</t>
+          <t>201534</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158478</t>
+          <t>179573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208266</t>
+          <t>225367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>256633</t>
+          <t>263538</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>226551</t>
+          <t>236387</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>286477</t>
+          <t>296430</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>332540</t>
+          <t>346257</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>311624</t>
+          <t>325898</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>352711</t>
+          <t>367911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>589173</t>
+          <t>609794</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>551150</t>
+          <t>572796</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>624153</t>
+          <t>648149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,21%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>261757</t>
+          <t>267109</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>231913</t>
+          <t>234217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>291839</t>
+          <t>294260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>181751</t>
+          <t>199552</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>161580</t>
+          <t>177898</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>202667</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>443507</t>
+          <t>466662</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>408527</t>
+          <t>428307</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>481530</t>
+          <t>503660</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514291</t>
+          <t>545809</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032680</t>
+          <t>1076456</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032680</t>
+          <t>1076456</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032680</t>
+          <t>1076456</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>184981</t>
+          <t>187762</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>166216</t>
+          <t>171011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202176</t>
+          <t>205235</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>242728</t>
+          <t>250083</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>227317</t>
+          <t>235308</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>257553</t>
+          <t>264606</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>427709</t>
+          <t>437846</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>399940</t>
+          <t>412014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>450086</t>
+          <t>458707</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>131069</t>
+          <t>128231</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113874</t>
+          <t>110758</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149834</t>
+          <t>144982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>106400</t>
+          <t>106298</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91575</t>
+          <t>91775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121811</t>
+          <t>121073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>237469</t>
+          <t>234529</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>215092</t>
+          <t>213668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>265238</t>
+          <t>260361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>179212</t>
+          <t>203117</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154811</t>
+          <t>177227</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202382</t>
+          <t>229414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>313004</t>
+          <t>272099</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>252209</t>
+          <t>250196</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>370893</t>
+          <t>291434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>492215</t>
+          <t>475216</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>431461</t>
+          <t>442610</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>567050</t>
+          <t>507777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>63,86%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>133345</t>
+          <t>170028</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110175</t>
+          <t>143731</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157746</t>
+          <t>195918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>162714</t>
+          <t>149862</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104825</t>
+          <t>130527</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>223509</t>
+          <t>171765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>296059</t>
+          <t>319891</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>221224</t>
+          <t>287330</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>356813</t>
+          <t>352497</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>86506</t>
+          <t>93995</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75764</t>
+          <t>81649</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98414</t>
+          <t>105855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>134635</t>
+          <t>141831</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124643</t>
+          <t>130187</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144370</t>
+          <t>152369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>221141</t>
+          <t>235825</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>204205</t>
+          <t>219009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>236593</t>
+          <t>252373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>92236</t>
+          <t>111670</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80328</t>
+          <t>99810</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102978</t>
+          <t>124016</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>74021</t>
+          <t>85384</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64286</t>
+          <t>74846</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84013</t>
+          <t>97028</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>166257</t>
+          <t>197054</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150805</t>
+          <t>180506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>183193</t>
+          <t>213870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>49,41%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>157496</t>
+          <t>155536</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>142376</t>
+          <t>139440</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>172504</t>
+          <t>170097</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,27 +12447,27 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>166210</t>
+          <t>170963</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>152285</t>
+          <t>156649</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>178385</t>
+          <t>183037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>323706</t>
+          <t>326500</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>304706</t>
+          <t>308639</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>342996</t>
+          <t>346384</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,81%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>112140</t>
+          <t>115171</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>97132</t>
+          <t>100610</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127260</t>
+          <t>131267</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,22 +12560,22 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>90846</t>
+          <t>92787</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78671</t>
+          <t>80713</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104771</t>
+          <t>107101</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>202986</t>
+          <t>207957</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>183696</t>
+          <t>188073</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>221986</t>
+          <t>225818</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>375182</t>
+          <t>439105</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>343935</t>
+          <t>410016</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>406477</t>
+          <t>468995</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>648576</t>
+          <t>533045</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>574384</t>
+          <t>508487</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>750678</t>
+          <t>558830</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1023758</t>
+          <t>972150</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>936183</t>
+          <t>927474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1178153</t>
+          <t>1007963</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>67,57%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>249097</t>
+          <t>280582</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>217802</t>
+          <t>250692</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>280344</t>
+          <t>309671</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>200689</t>
+          <t>239012</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>98587</t>
+          <t>213227</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>274881</t>
+          <t>263570</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>449786</t>
+          <t>519594</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>295391</t>
+          <t>483781</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>537361</t>
+          <t>564270</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>264248</t>
+          <t>299402</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>118177</t>
+          <t>272673</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>370408</t>
+          <t>331419</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>368952</t>
+          <t>419769</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>347674</t>
+          <t>393790</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>393683</t>
+          <t>445772</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>633200</t>
+          <t>719171</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>386999</t>
+          <t>679487</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>759340</t>
+          <t>756090</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>664472</t>
+          <t>498670</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>558312</t>
+          <t>466653</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>810543</t>
+          <t>525399</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>345899</t>
+          <t>410237</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>321168</t>
+          <t>384234</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>367177</t>
+          <t>436216</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1010372</t>
+          <t>908907</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>884232</t>
+          <t>871988</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1256573</t>
+          <t>948591</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>58,26%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1705627</t>
+          <t>1845298</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1322592</t>
+          <t>1778416</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1860030</t>
+          <t>1909063</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2422952</t>
+          <t>2364576</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2308673</t>
+          <t>2312258</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2627814</t>
+          <t>2418038</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4128578</t>
+          <t>4209874</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3690438</t>
+          <t>4126631</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4383430</t>
+          <t>4298084</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>59,15%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1754190</t>
+          <t>1687464</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1599787</t>
+          <t>1623699</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2137225</t>
+          <t>1754346</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1235646</t>
+          <t>1368665</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1030784</t>
+          <t>1315203</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1349925</t>
+          <t>1420983</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2989837</t>
+          <t>3056129</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2734985</t>
+          <t>2967919</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3427977</t>
+          <t>3139372</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
